--- a/testdata/round2.xlsx
+++ b/testdata/round2.xlsx
@@ -12,6 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="尾部空行" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="括号列名" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="高基数" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公式" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字典" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13291,4 +13293,330 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>部门</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>分母</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> A-1 </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>110</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A-2</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>120</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A-3 </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A-4</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A-5</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>200</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> B-1 </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>400</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>B-2</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>600</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>B-3</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>目标值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>